--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.11360576523502</v>
+        <v>4.405960936850691</v>
       </c>
       <c r="D2" t="n">
-        <v>26.48648078099476</v>
+        <v>4.30405312691165</v>
       </c>
       <c r="E2" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F2" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.62782704726104</v>
+        <v>5.627021895179919</v>
       </c>
       <c r="D3" t="n">
-        <v>33.33046670405857</v>
+        <v>5.416200839409517</v>
       </c>
       <c r="E3" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F3" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.925498318463179</v>
+        <v>1.612893476750267</v>
       </c>
       <c r="D4" t="n">
-        <v>21.80121163690375</v>
+        <v>3.542696890996859</v>
       </c>
       <c r="E4" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F4" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.8203064161148</v>
+        <v>3.708299792618656</v>
       </c>
       <c r="D5" t="n">
-        <v>27.11742165531467</v>
+        <v>4.406581018988634</v>
       </c>
       <c r="E5" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F5" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.2832519857548</v>
+        <v>3.133528447685154</v>
       </c>
       <c r="D6" t="n">
-        <v>32.10140183854904</v>
+        <v>5.21647779876422</v>
       </c>
       <c r="E6" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F6" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.09210365017687</v>
+        <v>1.802466843153741</v>
       </c>
       <c r="D7" t="n">
-        <v>11.05135734094009</v>
+        <v>1.795845567902765</v>
       </c>
       <c r="E7" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F7" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.805780165954286</v>
+        <v>1.105939276967572</v>
       </c>
       <c r="D8" t="n">
-        <v>9.055385138137417</v>
+        <v>1.47150008494733</v>
       </c>
       <c r="E8" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F8" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.03490832455455</v>
+        <v>2.605672602740115</v>
       </c>
       <c r="D9" t="n">
-        <v>17.27719794533029</v>
+        <v>2.807544666116172</v>
       </c>
       <c r="E9" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F9" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.34920646210259</v>
+        <v>5.906746050091671</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72021559305886</v>
+        <v>5.967035033872065</v>
       </c>
       <c r="E10" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F10" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>4.661071896825318</v>
+        <v>0.7574241832341142</v>
       </c>
       <c r="D11" t="n">
-        <v>27.73084924772409</v>
+        <v>4.506263002755166</v>
       </c>
       <c r="E11" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F11" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>4.659716853436102</v>
+        <v>0.7572039886833666</v>
       </c>
       <c r="D12" t="n">
-        <v>25.92048103028242</v>
+        <v>4.212078167420893</v>
       </c>
       <c r="E12" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F12" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.571308174774883</v>
+        <v>1.555337578400918</v>
       </c>
       <c r="D13" t="n">
-        <v>9.805952021505382</v>
+        <v>1.593467203494625</v>
       </c>
       <c r="E13" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F13" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9736190910404</v>
+        <v>0.320713102294065</v>
       </c>
       <c r="D14" t="n">
-        <v>30.70594296338547</v>
+        <v>4.989715731550139</v>
       </c>
       <c r="E14" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F14" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>10.92525107771492</v>
+        <v>1.775353300128675</v>
       </c>
       <c r="D15" t="n">
-        <v>11.11429362135827</v>
+        <v>1.806072713470719</v>
       </c>
       <c r="E15" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F15" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>7.5000062627638</v>
+        <v>1.218751017699118</v>
       </c>
       <c r="D16" t="n">
-        <v>22.76887344065244</v>
+        <v>3.699941934106022</v>
       </c>
       <c r="E16" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F16" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>30.83332525464828</v>
+        <v>5.010415353880346</v>
       </c>
       <c r="D17" t="n">
-        <v>7.31402064251829</v>
+        <v>1.188528354409222</v>
       </c>
       <c r="E17" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F17" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.07156930477934</v>
+        <v>5.211630012026642</v>
       </c>
       <c r="D18" t="n">
-        <v>15.8184866906105</v>
+        <v>2.570504087224205</v>
       </c>
       <c r="E18" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F18" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>19.75470569217412</v>
+        <v>3.210139674978294</v>
       </c>
       <c r="D19" t="n">
-        <v>34.36487224542591</v>
+        <v>5.584291739881711</v>
       </c>
       <c r="E19" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F19" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>38.13849310106185</v>
+        <v>6.197505128922551</v>
       </c>
       <c r="D20" t="n">
-        <v>10.31300976201778</v>
+        <v>1.675864086327889</v>
       </c>
       <c r="E20" t="n">
-        <v>11.64922926182339</v>
+        <v>1.892999755046301</v>
       </c>
       <c r="F20" t="n">
-        <v>9.557650534341008</v>
+        <v>1.553118211830414</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
